--- a/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
+++ b/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O250"/>
+  <dimension ref="A1:P250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -564,6 +565,11 @@
           <t>active</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>login_email</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -627,6 +633,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>maker@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -4865,7 +4876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -4931,44 +4942,51 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>7. Optional: login_email is the email the maker signs in with to edit their listing. It is added to Maker access automatically. One email can be used on several rows.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Do not include passwords, payment information, government IDs, or private notes in this file.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Allowed social domains</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Instagram: instagram.com  |  Facebook: facebook.com or fb.com  |  TikTok: tiktok.com</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
+++ b/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P250"/>
+  <dimension ref="A1:Q250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -487,6 +487,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -570,6 +571,11 @@
           <t>login_email</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>owner_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -638,6 +644,11 @@
           <t>maker@example.com</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Jane Maker</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -4876,7 +4887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -4949,44 +4960,51 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>8. Optional: owner_name is the owner's full name, shown on the profile as "Meet" and their name.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Do not include passwords, payment information, government IDs, or private notes in this file.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-    </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Allowed social domains</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Instagram: instagram.com  |  Facebook: facebook.com or fb.com  |  TikTok: tiktok.com</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
+++ b/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
@@ -610,12 +610,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://example.com</t>
+          <t>examplemaker.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/examplemaker</t>
+          <t>@examplemaker</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -4896,112 +4896,120 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>The Cannery Marketplace — One-Time Vendor Import</t>
+          <t>The Cannery Marketplace: Vendor Import (template version 3, October 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>How to use this file</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>1. Keep the header row unchanged. Fields marked with * are required.</t>
+          <t>1. Add one vendor per row. Delete the example row before importing real vendors.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2. Add one vendor per row. Delete the example row before importing real vendors.</t>
+          <t>2. Required for every row: name, category, short_bio (at least 20 characters), and an email (contact_email, or login_email if they are the same).</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>3. Social links must point to the matching service (Instagram, Facebook, or TikTok).</t>
+          <t>3. Everything else is optional, including website and social media.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>4. Separate multiple gallery image URLs with a vertical bar: URL 1 | URL 2. Maximum five gallery images.</t>
+          <t>4. Website: a full link or just the address, like examplemaker.com.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>5. Save as .xlsx, upload in Admin &gt; Vendor import, review all errors, then confirm the import.</t>
+          <t>5. Instagram, Facebook, TikTok: type the @handle (like @examplemaker) or paste the full link.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>6. Imported vendors are approved by the administrator and can appear publicly when Active is Yes.</t>
+          <t>6. login_email: the email the maker signs in with to edit their listing. It is added to Maker access automatically. One email can be used on several rows.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>7. Optional: login_email is the email the maker signs in with to edit their listing. It is added to Maker access automatically. One email can be used on several rows.</t>
+          <t>7. owner_name: the owner's full name, shown on the profile as "Meet" and their name.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>8. Optional: owner_name is the owner's full name, shown on the profile as "Meet" and their name.</t>
+          <t>8. Gallery images: separate several links with a vertical bar (|). Maximum five.</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>9. featured and active: Yes or No. display_order: a number; lower numbers show first.</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>10. Save as .xlsx, upload in the owner dashboard under Vendor import, fix any problems shown, then confirm.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Works with any version</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Columns can be in any order and any letter case, with or without the * marks. Older versions of this template still import. Columns the site does not recognize are listed and skipped, so adding your own notes column is safe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Do not include passwords, payment information, government IDs, or private notes in this file.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-    </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Allowed social domains</t>
-        </is>
-      </c>
+      <c r="A17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Instagram: instagram.com  |  Facebook: facebook.com or fb.com  |  TikTok: tiktok.com</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>

--- a/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
+++ b/client/public/downloads/Vendor-Bulk-Import-Template.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>owner_name</t>
+          <t>maker_full_name</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2. Required for every row: name, category, short_bio (at least 20 characters), and an email (contact_email, or login_email if they are the same).</t>
+          <t>2. Required for every row: name (the business name), category, short_bio (at least 20 characters), and an email (contact_email, or login_email if they are the same).</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>7. owner_name: the owner's full name, shown on the profile as "Meet" and their name.</t>
+          <t>7. maker_full_name: the maker's full name (the person behind the work), shown on the profile as "Meet" and their name. Older files that use owner_name still work.</t>
         </is>
       </c>
     </row>
